--- a/IlNufuslarii.xlsx
+++ b/IlNufuslarii.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1633-t5" sheetId="2" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'1633-t5'!$A$1:$B$83</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'1633-t5'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -282,7 +282,7 @@
     <t>Nüfus</t>
   </si>
   <si>
-    <t xml:space="preserve">Net Göç</t>
+    <t>Net Goc</t>
   </si>
   <si>
     <t xml:space="preserve">Net GC6C'</t>
@@ -293,7 +293,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="###\ ###\ ###"/>
+    <numFmt numFmtId="164" formatCode="###\ ###\ ###"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -361,13 +361,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -681,8 +681,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -1600,7 +1600,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
     <oddFooter>&amp;L&amp;C&amp;R&amp;P/&amp;N</oddFooter>
   </headerFooter>
